--- a/membership_forms/040_assp_toastmasters_club_member_survey_sep_2021--membership_forms.xlsx
+++ b/membership_forms/040_assp_toastmasters_club_member_survey_sep_2021--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>possibly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>possibly</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>possibly</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>possibly</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1868,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>not_interested</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>not interested</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>workshop_interest_choices</t>
+          <t>improvement_areas_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>not_interested</t>
+          <t>meeting_structure</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>not interested</t>
+          <t>Meeting structure</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>meeting_structure</t>
+          <t>guest_speakers</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Meeting structure</t>
+          <t>Guest speakers</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>guest_speakers</t>
+          <t>networking_opportunities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Guest speakers</t>
+          <t>Networking opportunities</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>networking_opportunities</t>
+          <t>meeting_length</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Networking opportunities</t>
+          <t>Meeting length</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>meeting_length</t>
+          <t>meeting_location</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Meeting length</t>
+          <t>Meeting location</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>meeting_location</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Meeting location</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>educational_content</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Educational content</t>
         </is>
       </c>
     </row>
@@ -2004,29 +2004,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>educational_content</t>
+          <t>leadership_development</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Educational content</t>
+          <t>Leadership development</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>improvement_areas_choices</t>
+          <t>online_resources_utilization_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>leadership_development</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Leadership development</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2089,29 +2089,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>online_resources_utilization_choices</t>
+          <t>mentor_assignment_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2140,29 +2140,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>not_interested</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Not interested</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>mentor_assignment_choices</t>
+          <t>mentoring_interest_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>not_interested</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Not interested</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>as_a_mentee</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>as a mentee</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>as_a_mentee</t>
+          <t>as_a_mentor</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>as a mentee</t>
+          <t>as a mentor</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>as_both</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>as both</t>
         </is>
       </c>
     </row>
@@ -2225,63 +2225,63 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>as_a_mentor</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>as a mentor</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mentoring_interest_choices</t>
+          <t>special_interest_groups_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mentoring_interest_choices</t>
+          <t>special_interest_groups_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>as_both</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>as both</t>
+          <t>Storytelling</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mentoring_interest_choices</t>
+          <t>special_interest_groups_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>business_presentations</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Business presentations</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>technical_speaking</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Technical speaking</t>
         </is>
       </c>
     </row>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>storytelling</t>
+          <t>humorous_speaking</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Storytelling</t>
+          <t>Humorous speaking</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>business_presentations</t>
+          <t>table_topics</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Business presentations</t>
+          <t>Table Topics</t>
         </is>
       </c>
     </row>
@@ -2344,61 +2344,10 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>technical_speaking</t>
+          <t>advanced_communication</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
-        <is>
-          <t>Technical speaking</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>special_interest_groups_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>humorous_speaking</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Humorous speaking</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>special_interest_groups_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>table_topics</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Table Topics</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>special_interest_groups_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>advanced_communication</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
         <is>
           <t>Advanced communication</t>
         </is>
